--- a/hardware/luxdmx_CPL.xlsx
+++ b/hardware/luxdmx_CPL.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E90"/>
+  <dimension ref="A1:E98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -640,12 +640,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>56.1811mm</t>
+          <t>64.0375mm</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-14.1064mm</t>
+          <t>-11.8872mm</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -655,7 +655,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -667,12 +667,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>66.2189mm</t>
+          <t>59.7189mm</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-12.6250mm</t>
+          <t>-11.9750mm</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -721,12 +721,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>70.3856mm</t>
+          <t>84.0556mm</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>31.0683mm</t>
+          <t>31.0790mm</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -775,12 +775,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>71.0995mm</t>
+          <t>84.7695mm</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>36.0306mm</t>
+          <t>36.0413mm</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -856,12 +856,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>53.1197mm</t>
+          <t>55.7189mm</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.1583mm</t>
+          <t>-9.4450mm</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
@@ -883,12 +883,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>70.5331mm</t>
+          <t>84.2031mm</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.1583mm</t>
+          <t>0.1690mm</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -910,12 +910,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>71.5389mm</t>
+          <t>85.2089mm</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>5.3941mm</t>
+          <t>5.4048mm</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1261,12 +1261,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>74.6564mm</t>
+          <t>88.3264mm</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>32.0250mm</t>
+          <t>32.0357mm</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1315,12 +1315,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>51.2189mm</t>
+          <t>61.2189mm</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>-9.9250mm</t>
+          <t>-7.9250mm</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>180</t>
         </is>
       </c>
     </row>
@@ -1477,12 +1477,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>75.2814mm</t>
+          <t>88.9514mm</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1.0750mm</t>
+          <t>1.0857mm</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>37.2189mm</t>
+          <t>40.7189mm</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>-23.3250mm</t>
+          <t>-22.3250mm</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1526,17 +1526,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>FB1</t>
+          <t>F2</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>51.6389mm</t>
+          <t>95.7189mm</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>35.5750mm</t>
+          <t>36.1050mm</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>FB2</t>
+          <t>F3</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>71.5932mm</t>
+          <t>95.7189mm</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>39.7476mm</t>
+          <t>25.6050mm</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1573,24 +1573,24 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>FB3</t>
+          <t>F4</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>71.9558mm</t>
+          <t>95.7189mm</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>9.1748mm</t>
+          <t>5.0450mm</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1600,24 +1600,24 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>J1</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>88.7189mm</t>
+          <t>95.7189mm</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>29.0750mm</t>
+          <t>-5.9550mm</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1627,24 +1627,24 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>J2</t>
+          <t>FB1</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>44.7189mm</t>
+          <t>51.6389mm</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>-22.2350mm</t>
+          <t>35.5750mm</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1661,17 +1661,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>J3</t>
+          <t>FB2</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>8.9589mm</t>
+          <t>85.2632mm</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>-6.4250mm</t>
+          <t>39.7583mm</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1688,17 +1688,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>J4</t>
+          <t>FB3</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>47.2189mm</t>
+          <t>85.6258mm</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>8.0750mm</t>
+          <t>9.1855mm</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1708,24 +1708,24 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>J5</t>
+          <t>J1</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>88.8764mm</t>
+          <t>108.7189mm</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>-1.9250mm</t>
+          <t>29.0750mm</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1742,17 +1742,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>J6</t>
+          <t>J2</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>47.2189mm</t>
+          <t>49.3889mm</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>21.5750mm</t>
+          <t>-22.2350mm</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1762,24 +1762,24 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>J7</t>
+          <t>J3</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>73.4189mm</t>
+          <t>8.9589mm</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>25.4500mm</t>
+          <t>-6.4250mm</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1796,17 +1796,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>J8</t>
+          <t>J4</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>72.9189mm</t>
+          <t>47.2189mm</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>-6.0500mm</t>
+          <t>8.0750mm</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1816,24 +1816,24 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>180</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>J5</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>66.2189mm</t>
+          <t>108.8764mm</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>-16.5250mm</t>
+          <t>-1.9250mm</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1843,24 +1843,24 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>270</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>J6</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>76.2689mm</t>
+          <t>47.2189mm</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>39.6750mm</t>
+          <t>21.5750mm</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1870,24 +1870,24 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>180</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>J7</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>76.7189mm</t>
+          <t>87.0889mm</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>9.0750mm</t>
+          <t>25.4607mm</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1904,17 +1904,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>PS1</t>
+          <t>J8</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>60.9089mm</t>
+          <t>86.5889mm</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>35.5750mm</t>
+          <t>-6.0393mm</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1931,17 +1931,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>PS2</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>61.2664mm</t>
+          <t>61.6189mm</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>5.2450mm</t>
+          <t>-21.9250mm</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1958,17 +1958,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>42.6689mm</t>
+          <t>89.9389mm</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>37.5125mm</t>
+          <t>39.6857mm</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1978,24 +1978,24 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>42.6689mm</t>
+          <t>90.3889mm</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>32.0125mm</t>
+          <t>9.0857mm</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2005,24 +2005,24 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>PS1</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>6.5025mm</t>
+          <t>74.5789mm</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>16.1790mm</t>
+          <t>35.5857mm</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2039,17 +2039,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>R10</t>
+          <t>PS2</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>62.7189mm</t>
+          <t>74.9364mm</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>-19.4350mm</t>
+          <t>5.2557mm</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2059,24 +2059,24 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>R11</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>59.5972mm</t>
+          <t>42.6689mm</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>-19.4350mm</t>
+          <t>37.5125mm</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2086,24 +2086,24 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>270</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>76.3064mm</t>
+          <t>42.6689mm</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>36.0750mm</t>
+          <t>32.0125mm</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2113,24 +2113,24 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>270</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>R13</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>24.2189mm</t>
+          <t>6.5025mm</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>45.5750mm</t>
+          <t>16.1790mm</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2140,24 +2140,24 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>R14</t>
+          <t>R10</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>26.7189mm</t>
+          <t>58.7089mm</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>45.5750mm</t>
+          <t>-18.4250mm</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2167,24 +2167,24 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>R15</t>
+          <t>R11</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>29.2189mm</t>
+          <t>58.7089mm</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>45.5750mm</t>
+          <t>-15.3033mm</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2194,24 +2194,24 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>R16</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>31.7189mm</t>
+          <t>89.9764mm</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>45.5650mm</t>
+          <t>36.0857mm</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2221,19 +2221,19 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>R17</t>
+          <t>R13</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>34.2189mm</t>
+          <t>24.2189mm</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2255,17 +2255,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>R18</t>
+          <t>R14</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>20.4231mm</t>
+          <t>26.7189mm</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>-3.3763mm</t>
+          <t>45.5750mm</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2275,24 +2275,24 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>R19</t>
+          <t>R15</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>76.8064mm</t>
+          <t>29.2189mm</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>5.5750mm</t>
+          <t>45.5750mm</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2302,24 +2302,24 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R16</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>18.1501mm</t>
+          <t>31.7189mm</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>44.5248mm</t>
+          <t>45.5650mm</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2329,24 +2329,24 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R17</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>30.1398mm</t>
+          <t>34.2189mm</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>1.9487mm</t>
+          <t>45.5750mm</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2356,24 +2356,24 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>R4</t>
+          <t>R18</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>9.7089mm</t>
+          <t>20.4231mm</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>-16.4250mm</t>
+          <t>-3.3763mm</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2390,17 +2390,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>R19</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>3.0686mm</t>
+          <t>90.4764mm</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>4.9674mm</t>
+          <t>5.5857mm</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2417,17 +2417,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>R6</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>37.7885mm</t>
+          <t>18.1501mm</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>36.4263mm</t>
+          <t>44.5248mm</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2437,24 +2437,24 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>R7</t>
+          <t>R20</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>37.9994mm</t>
+          <t>82.3789mm</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>32.4249mm</t>
+          <t>33.5857mm</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2464,24 +2464,24 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>R8</t>
+          <t>R21</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>42.2289mm</t>
+          <t>81.8889mm</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>-16.1350mm</t>
+          <t>39.0757mm</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>270</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>R9</t>
+          <t>R22</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>47.0389mm</t>
+          <t>82.3789mm</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>-14.1050mm</t>
+          <t>8.0857mm</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2518,24 +2518,24 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>270</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>SW1</t>
+          <t>R23</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>11.2189mm</t>
+          <t>82.3789mm</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>46.8750mm</t>
+          <t>2.5857mm</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2545,24 +2545,24 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>180</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>SW2</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>15.2189mm</t>
+          <t>30.1398mm</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>46.8750mm</t>
+          <t>1.9487mm</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -2572,24 +2572,24 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>U1</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>10.4889mm</t>
+          <t>9.7089mm</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>32.5750mm</t>
+          <t>-16.4250mm</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -2599,24 +2599,24 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>U2</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>32.4689mm</t>
+          <t>3.0686mm</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>-8.6750mm</t>
+          <t>4.9674mm</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -2626,24 +2626,24 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>U3</t>
+          <t>R6</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>31.7189mm</t>
+          <t>37.7885mm</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>34.5750mm</t>
+          <t>36.4263mm</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2653,24 +2653,24 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>U4</t>
+          <t>R7</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>60.8021mm</t>
+          <t>37.9994mm</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>-15.9759mm</t>
+          <t>32.4249mm</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -2687,17 +2687,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>U5</t>
+          <t>R8</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>61.6789mm</t>
+          <t>46.8989mm</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>27.2050mm</t>
+          <t>-16.1350mm</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2707,24 +2707,24 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>U6</t>
+          <t>R9</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>61.8264mm</t>
+          <t>51.7089mm</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>-3.7050mm</t>
+          <t>-14.1050mm</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -2734,24 +2734,24 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>U7</t>
+          <t>SW1</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>27.2189mm</t>
+          <t>11.2189mm</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>12.5750mm</t>
+          <t>46.8750mm</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -2761,24 +2761,24 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>270</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>U8</t>
+          <t>SW2</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>41.7192mm</t>
+          <t>15.2189mm</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>-12.2524mm</t>
+          <t>46.8750mm</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -2788,24 +2788,24 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>270</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>U1</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>6.7189mm</t>
+          <t>10.4889mm</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>6.5750mm</t>
+          <t>32.5750mm</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -2815,32 +2815,248 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
+          <t>U2</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>32.4689mm</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>-8.6750mm</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>U3</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>31.7189mm</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>34.5750mm</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>U4</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>62.1680mm</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>-16.5082mm</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>U5</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>75.3489mm</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>27.2157mm</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>U6</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>75.4964mm</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>-3.6943mm</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>U7</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>27.2189mm</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>12.5750mm</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>U8</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>45.3564mm</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>-12.2524mm</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>U9</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>6.7189mm</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>6.5750mm</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
           <t>Y1</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
+      <c r="B98" t="inlineStr">
         <is>
           <t>31.9605mm</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
+      <c r="C98" t="inlineStr">
         <is>
           <t>-17.3174mm</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/hardware/luxdmx_CPL.xlsx
+++ b/hardware/luxdmx_CPL.xlsx
@@ -456,7 +456,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>20.6511mm</t>
+          <t>18.9011mm</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -478,12 +478,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>26.2532mm</t>
+          <t>38.8510mm</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.4711mm</t>
+          <t>-7.9250mm</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -505,12 +505,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>24.6337mm</t>
+          <t>29.7189mm</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-6.5993mm</t>
+          <t>-14.4050mm</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -520,7 +520,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>270</t>
         </is>
       </c>
     </row>
@@ -532,12 +532,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>36.6917mm</t>
+          <t>40.8710mm</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-16.9242mm</t>
+          <t>-7.9250mm</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -547,7 +547,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>180</t>
         </is>
       </c>
     </row>
@@ -559,12 +559,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>27.3515mm</t>
+          <t>39.8310mm</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-17.7241mm</t>
+          <t>-2.9250mm</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -586,12 +586,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>20.1139mm</t>
+          <t>13.7189mm</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-7.9919mm</t>
+          <t>4.6150mm</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
@@ -613,12 +613,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>25.6602mm</t>
+          <t>23.2189mm</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>34.9368mm</t>
+          <t>34.0750mm</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -640,12 +640,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>64.0375mm</t>
+          <t>76.9142mm</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-11.8872mm</t>
+          <t>-23.4250mm</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -655,7 +655,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>180</t>
         </is>
       </c>
     </row>
@@ -667,12 +667,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>59.7189mm</t>
+          <t>73.9142mm</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-11.9750mm</t>
+          <t>-15.4250mm</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -694,12 +694,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>52.9722mm</t>
+          <t>67.7189mm</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>31.0683mm</t>
+          <t>31.0550mm</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>270</t>
         </is>
       </c>
     </row>
@@ -721,12 +721,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>84.0556mm</t>
+          <t>81.7189mm</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>31.0790mm</t>
+          <t>33.5950mm</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
@@ -748,12 +748,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>7.0650mm</t>
+          <t>7.7689mm</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>19.5266mm</t>
+          <t>16.0750mm</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>51.3189mm</t>
+          <t>65.7439mm</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>38.8750mm</t>
+          <t>34.0750mm</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -817,7 +817,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>180</t>
         </is>
       </c>
     </row>
@@ -829,12 +829,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>21.1996mm</t>
+          <t>19.7389mm</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.4461mm</t>
+          <t>-2.9250mm</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -856,12 +856,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>55.7189mm</t>
+          <t>67.7389mm</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-9.4450mm</t>
+          <t>1.0750mm</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>180</t>
         </is>
       </c>
     </row>
@@ -883,12 +883,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>84.2031mm</t>
+          <t>81.7189mm</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.1690mm</t>
+          <t>2.5750mm</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
@@ -937,12 +937,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>47.3189mm</t>
+          <t>66.2439mm</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>34.0750mm</t>
+          <t>4.1000mm</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>180</t>
         </is>
       </c>
     </row>
@@ -964,12 +964,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>44.2189mm</t>
+          <t>21.5189mm</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-1.4250mm</t>
+          <t>13.0500mm</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>180</t>
         </is>
       </c>
     </row>
@@ -991,12 +991,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>13.6720mm</t>
+          <t>30.7689mm</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>6.2447mm</t>
+          <t>3.5500mm</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>180</t>
         </is>
       </c>
     </row>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>12.1250mm</t>
+          <t>15.5750mm</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1050,7 +1050,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>17.7135mm</t>
+          <t>15.9635mm</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>7.4177mm</t>
+          <t>4.2189mm</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>3.9670mm</t>
+          <t>5.4103mm</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1087,7 +1087,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>270</t>
         </is>
       </c>
     </row>
@@ -1099,12 +1099,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>10.0189mm</t>
+          <t>8.2189mm</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>6.5750mm</t>
+          <t>5.4103mm</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>270</t>
         </is>
       </c>
     </row>
@@ -1126,12 +1126,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>24.6337mm</t>
+          <t>34.1989mm</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-10.7507mm</t>
+          <t>-13.4250mm</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1153,12 +1153,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>24.2104mm</t>
+          <t>34.1989mm</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-13.7374mm</t>
+          <t>-14.4250mm</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1180,12 +1180,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>24.6909mm</t>
+          <t>32.2189mm</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>-3.6118mm</t>
+          <t>-14.4050mm</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>270</t>
         </is>
       </c>
     </row>
@@ -1207,12 +1207,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>34.6218mm</t>
+          <t>24.2389mm</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>-1.3550mm</t>
+          <t>-5.4250mm</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>180</t>
         </is>
       </c>
     </row>
@@ -1234,12 +1234,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>30.0735mm</t>
+          <t>28.7189mm</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>-1.2230mm</t>
+          <t>-14.4050mm</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>270</t>
         </is>
       </c>
     </row>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>27.2189mm</t>
+          <t>53.2189mm</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>25.0750mm</t>
+          <t>20.0500mm</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>270</t>
         </is>
       </c>
     </row>
@@ -1315,12 +1315,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>61.2189mm</t>
+          <t>65.9642mm</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>-7.9250mm</t>
+          <t>-21.4250mm</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>270</t>
         </is>
       </c>
     </row>
@@ -1504,12 +1504,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>40.7189mm</t>
+          <t>54.6189mm</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>-22.3250mm</t>
+          <t>-20.4250mm</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>180</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>25.6050mm</t>
+          <t>27.0450mm</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>-5.9550mm</t>
+          <t>-4.4550mm</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1639,12 +1639,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>51.6389mm</t>
+          <t>66.2189mm</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>35.5750mm</t>
+          <t>36.5750mm</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>180</t>
         </is>
       </c>
     </row>
@@ -1666,12 +1666,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>85.2632mm</t>
+          <t>83.7814mm</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>39.7583mm</t>
+          <t>31.0750mm</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1681,7 +1681,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>180</t>
         </is>
       </c>
     </row>
@@ -1693,12 +1693,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>85.6258mm</t>
+          <t>84.1564mm</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>9.1855mm</t>
+          <t>0.5750mm</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>180</t>
         </is>
       </c>
     </row>
@@ -1747,12 +1747,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>49.3889mm</t>
+          <t>44.5289mm</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>-22.2350mm</t>
+          <t>-22.2186mm</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>47.2189mm</t>
+          <t>15.4189mm</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>8.0750mm</t>
+          <t>46.7000mm</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1855,12 +1855,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>47.2189mm</t>
+          <t>51.9189mm</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>21.5750mm</t>
+          <t>34.2000mm</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>87.0889mm</t>
+          <t>89.7189mm</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>25.4607mm</t>
+          <t>25.0750mm</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>86.5889mm</t>
+          <t>89.4189mm</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>61.6189mm</t>
+          <t>72.4642mm</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>-21.9250mm</t>
+          <t>-19.4250mm</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
@@ -1968,7 +1968,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>39.6857mm</t>
+          <t>39.0750mm</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1995,7 +1995,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>9.0857mm</t>
+          <t>8.0857mm</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2071,12 +2071,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>42.6689mm</t>
+          <t>40.2276mm</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>37.5125mm</t>
+          <t>36.6507mm</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2098,12 +2098,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>42.6689mm</t>
+          <t>40.2276mm</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>32.0125mm</t>
+          <t>31.1507mm</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>6.5025mm</t>
+          <t>2.2089mm</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>16.1790mm</t>
+          <t>17.3250mm</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>58.7089mm</t>
+          <t>80.4742mm</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>-18.4250mm</t>
+          <t>-17.9250mm</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2167,7 +2167,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>180</t>
         </is>
       </c>
     </row>
@@ -2179,12 +2179,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>58.7089mm</t>
+          <t>80.4742mm</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>-15.3033mm</t>
+          <t>-21.0467mm</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>180</t>
         </is>
       </c>
     </row>
@@ -2368,12 +2368,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>20.4231mm</t>
+          <t>14.7189mm</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>-3.3763mm</t>
+          <t>4.5850mm</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2383,7 +2383,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
@@ -2422,12 +2422,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>18.1501mm</t>
+          <t>22.2089mm</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>44.5248mm</t>
+          <t>41.0750mm</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>82.3789mm</t>
+          <t>83.7089mm</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>33.5857mm</t>
+          <t>33.0750mm</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>82.3789mm</t>
+          <t>83.7089mm</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2.5857mm</t>
+          <t>2.5750mm</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2557,12 +2557,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>30.1398mm</t>
+          <t>24.2089mm</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>1.9487mm</t>
+          <t>-7.9250mm</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>9.7089mm</t>
+          <t>31.2189mm</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>-16.4250mm</t>
+          <t>-14.4350mm</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -2599,7 +2599,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
@@ -2611,12 +2611,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>3.0686mm</t>
+          <t>0.7189mm</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>4.9674mm</t>
+          <t>4.5850mm</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>270</t>
         </is>
       </c>
     </row>
@@ -2638,12 +2638,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>37.7885mm</t>
+          <t>35.3472mm</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>36.4263mm</t>
+          <t>35.5645mm</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2665,12 +2665,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>37.9994mm</t>
+          <t>35.5581mm</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>32.4249mm</t>
+          <t>31.5631mm</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -2692,12 +2692,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>46.8989mm</t>
+          <t>50.1690mm</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>-16.1350mm</t>
+          <t>-14.3761mm</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2707,7 +2707,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>180</t>
         </is>
       </c>
     </row>
@@ -2719,12 +2719,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>51.7089mm</t>
+          <t>57.1690mm</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>-14.1050mm</t>
+          <t>-14.3761mm</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -2746,12 +2746,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>11.2189mm</t>
+          <t>87.7189mm</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>46.8750mm</t>
+          <t>-21.9250mm</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -2773,12 +2773,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>15.2189mm</t>
+          <t>94.2189mm</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>46.8750mm</t>
+          <t>-21.9250mm</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -2805,7 +2805,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>32.5750mm</t>
+          <t>30.8250mm</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>32.4689mm</t>
+          <t>30.9689mm</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>-8.6750mm</t>
+          <t>-6.6750mm</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>270</t>
         </is>
       </c>
     </row>
@@ -2854,12 +2854,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>31.7189mm</t>
+          <t>29.2776mm</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>34.5750mm</t>
+          <t>33.7132mm</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -2881,12 +2881,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>62.1680mm</t>
+          <t>77.1642mm</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>-16.5082mm</t>
+          <t>-19.3750mm</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -2896,7 +2896,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>180</t>
         </is>
       </c>
     </row>
@@ -2962,12 +2962,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>27.2189mm</t>
+          <t>38.0389mm</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>12.5750mm</t>
+          <t>15.0500mm</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>45.3564mm</t>
+          <t>53.8165mm</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>-12.2524mm</t>
+          <t>-13.9261mm</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3016,12 +3016,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>6.7189mm</t>
+          <t>5.9789mm</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>6.5750mm</t>
+          <t>10.8250mm</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3043,12 +3043,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>31.9605mm</t>
+          <t>40.1510mm</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>-17.3174mm</t>
+          <t>-5.3000mm</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>

--- a/hardware/luxdmx_CPL.xlsx
+++ b/hardware/luxdmx_CPL.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E90"/>
+  <dimension ref="A1:E98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,7 +456,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>20.6511mm</t>
+          <t>18.9011mm</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -478,12 +478,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>26.2532mm</t>
+          <t>38.8510mm</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.4711mm</t>
+          <t>-7.9250mm</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -505,12 +505,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>24.6337mm</t>
+          <t>29.7189mm</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-6.5993mm</t>
+          <t>-14.4050mm</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -520,7 +520,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>270</t>
         </is>
       </c>
     </row>
@@ -532,12 +532,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>36.6917mm</t>
+          <t>40.8710mm</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-16.9242mm</t>
+          <t>-7.9250mm</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -547,7 +547,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>180</t>
         </is>
       </c>
     </row>
@@ -559,12 +559,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>27.3515mm</t>
+          <t>39.8310mm</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-17.7241mm</t>
+          <t>-2.9250mm</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -586,12 +586,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>20.1139mm</t>
+          <t>13.7189mm</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-7.9919mm</t>
+          <t>4.6150mm</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
@@ -613,12 +613,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>25.6602mm</t>
+          <t>23.2189mm</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>34.9368mm</t>
+          <t>34.0750mm</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -640,12 +640,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>56.1811mm</t>
+          <t>76.9142mm</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-14.1064mm</t>
+          <t>-23.4250mm</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -655,7 +655,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>180</t>
         </is>
       </c>
     </row>
@@ -667,12 +667,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>66.2189mm</t>
+          <t>73.9142mm</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-12.6250mm</t>
+          <t>-15.4250mm</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -694,12 +694,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>52.9722mm</t>
+          <t>67.7189mm</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>31.0683mm</t>
+          <t>31.0550mm</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>270</t>
         </is>
       </c>
     </row>
@@ -721,12 +721,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>70.3856mm</t>
+          <t>81.7189mm</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>31.0683mm</t>
+          <t>33.5950mm</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
@@ -748,12 +748,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>7.0650mm</t>
+          <t>7.7689mm</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>19.5266mm</t>
+          <t>16.0750mm</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -775,12 +775,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>71.0995mm</t>
+          <t>84.7695mm</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>36.0306mm</t>
+          <t>36.0413mm</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>51.3189mm</t>
+          <t>65.7439mm</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>38.8750mm</t>
+          <t>34.0750mm</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -817,7 +817,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>180</t>
         </is>
       </c>
     </row>
@@ -829,12 +829,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>21.1996mm</t>
+          <t>19.7389mm</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.4461mm</t>
+          <t>-2.9250mm</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -856,12 +856,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>53.1197mm</t>
+          <t>67.7389mm</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.1583mm</t>
+          <t>1.0750mm</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>180</t>
         </is>
       </c>
     </row>
@@ -883,12 +883,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>70.5331mm</t>
+          <t>81.7189mm</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.1583mm</t>
+          <t>2.5750mm</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
@@ -910,12 +910,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>71.5389mm</t>
+          <t>85.2089mm</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>5.3941mm</t>
+          <t>5.4048mm</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -937,12 +937,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>47.3189mm</t>
+          <t>66.2439mm</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>34.0750mm</t>
+          <t>4.1000mm</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>180</t>
         </is>
       </c>
     </row>
@@ -964,12 +964,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>44.2189mm</t>
+          <t>21.5189mm</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-1.4250mm</t>
+          <t>13.0500mm</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>180</t>
         </is>
       </c>
     </row>
@@ -991,12 +991,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>13.6720mm</t>
+          <t>30.7689mm</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>6.2447mm</t>
+          <t>3.5500mm</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>180</t>
         </is>
       </c>
     </row>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>12.1250mm</t>
+          <t>15.5750mm</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1050,7 +1050,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>17.7135mm</t>
+          <t>15.9635mm</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>7.4177mm</t>
+          <t>4.2189mm</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>3.9670mm</t>
+          <t>5.4103mm</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1087,7 +1087,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>270</t>
         </is>
       </c>
     </row>
@@ -1099,12 +1099,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>10.0189mm</t>
+          <t>8.2189mm</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>6.5750mm</t>
+          <t>5.4103mm</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>270</t>
         </is>
       </c>
     </row>
@@ -1126,12 +1126,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>24.6337mm</t>
+          <t>34.1989mm</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-10.7507mm</t>
+          <t>-13.4250mm</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1153,12 +1153,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>24.2104mm</t>
+          <t>34.1989mm</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-13.7374mm</t>
+          <t>-14.4250mm</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1180,12 +1180,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>24.6909mm</t>
+          <t>32.2189mm</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>-3.6118mm</t>
+          <t>-14.4050mm</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>270</t>
         </is>
       </c>
     </row>
@@ -1207,12 +1207,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>34.6218mm</t>
+          <t>24.2389mm</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>-1.3550mm</t>
+          <t>-5.4250mm</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>180</t>
         </is>
       </c>
     </row>
@@ -1234,12 +1234,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>30.0735mm</t>
+          <t>28.7189mm</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>-1.2230mm</t>
+          <t>-14.4050mm</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>270</t>
         </is>
       </c>
     </row>
@@ -1261,12 +1261,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>74.6564mm</t>
+          <t>88.3264mm</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>32.0250mm</t>
+          <t>32.0357mm</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>27.2189mm</t>
+          <t>53.2189mm</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>25.0750mm</t>
+          <t>20.0500mm</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>270</t>
         </is>
       </c>
     </row>
@@ -1315,12 +1315,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>51.2189mm</t>
+          <t>65.9642mm</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>-9.9250mm</t>
+          <t>-21.4250mm</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>270</t>
         </is>
       </c>
     </row>
@@ -1477,12 +1477,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>75.2814mm</t>
+          <t>88.9514mm</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1.0750mm</t>
+          <t>1.0857mm</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>37.2189mm</t>
+          <t>54.6189mm</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>-23.3250mm</t>
+          <t>-20.4250mm</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1519,24 +1519,24 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>180</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>FB1</t>
+          <t>F2</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>51.6389mm</t>
+          <t>95.7189mm</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>35.5750mm</t>
+          <t>36.1050mm</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>FB2</t>
+          <t>F3</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>71.5932mm</t>
+          <t>95.7189mm</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>39.7476mm</t>
+          <t>27.0450mm</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1573,24 +1573,24 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>FB3</t>
+          <t>F4</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>71.9558mm</t>
+          <t>95.7189mm</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>9.1748mm</t>
+          <t>5.0450mm</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1600,24 +1600,24 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>J1</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>88.7189mm</t>
+          <t>95.7189mm</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>29.0750mm</t>
+          <t>-4.4550mm</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1627,24 +1627,24 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>J2</t>
+          <t>FB1</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>44.7189mm</t>
+          <t>66.2189mm</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>-22.2350mm</t>
+          <t>36.5750mm</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1654,24 +1654,24 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>180</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>J3</t>
+          <t>FB2</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>8.9589mm</t>
+          <t>83.7814mm</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>-6.4250mm</t>
+          <t>31.0750mm</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1681,24 +1681,24 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>180</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>J4</t>
+          <t>FB3</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>47.2189mm</t>
+          <t>84.1564mm</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>8.0750mm</t>
+          <t>0.5750mm</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1715,17 +1715,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>J5</t>
+          <t>J1</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>88.8764mm</t>
+          <t>108.7189mm</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>-1.9250mm</t>
+          <t>29.0750mm</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1742,17 +1742,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>J6</t>
+          <t>J2</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>47.2189mm</t>
+          <t>44.5289mm</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>21.5750mm</t>
+          <t>-22.2186mm</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1762,24 +1762,24 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>J7</t>
+          <t>J3</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>73.4189mm</t>
+          <t>8.9589mm</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>25.4500mm</t>
+          <t>-6.4250mm</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1796,17 +1796,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>J8</t>
+          <t>J4</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>72.9189mm</t>
+          <t>15.4189mm</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>-6.0500mm</t>
+          <t>46.7000mm</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1816,24 +1816,24 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>180</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>J5</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>66.2189mm</t>
+          <t>108.8764mm</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>-16.5250mm</t>
+          <t>-1.9250mm</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1843,24 +1843,24 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>270</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>J6</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>76.2689mm</t>
+          <t>51.9189mm</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>39.6750mm</t>
+          <t>34.2000mm</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1870,24 +1870,24 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>180</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>J7</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>76.7189mm</t>
+          <t>89.7189mm</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>9.0750mm</t>
+          <t>25.0750mm</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1904,17 +1904,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>PS1</t>
+          <t>J8</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>60.9089mm</t>
+          <t>89.4189mm</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>35.5750mm</t>
+          <t>-6.0393mm</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1931,17 +1931,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>PS2</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>61.2664mm</t>
+          <t>72.4642mm</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>5.2450mm</t>
+          <t>-19.4250mm</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1951,24 +1951,24 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>42.6689mm</t>
+          <t>89.9389mm</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>37.5125mm</t>
+          <t>39.0750mm</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1978,24 +1978,24 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>42.6689mm</t>
+          <t>90.3889mm</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>32.0125mm</t>
+          <t>8.0857mm</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2005,24 +2005,24 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>PS1</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>6.5025mm</t>
+          <t>74.5789mm</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>16.1790mm</t>
+          <t>35.5857mm</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2039,17 +2039,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>R10</t>
+          <t>PS2</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>62.7189mm</t>
+          <t>74.9364mm</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>-19.4350mm</t>
+          <t>5.2557mm</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2059,24 +2059,24 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>R11</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>59.5972mm</t>
+          <t>40.2276mm</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>-19.4350mm</t>
+          <t>36.6507mm</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2086,24 +2086,24 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>270</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>76.3064mm</t>
+          <t>40.2276mm</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>36.0750mm</t>
+          <t>31.1507mm</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2113,24 +2113,24 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>270</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>R13</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>24.2189mm</t>
+          <t>2.2089mm</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>45.5750mm</t>
+          <t>17.3250mm</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2140,24 +2140,24 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>R14</t>
+          <t>R10</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>26.7189mm</t>
+          <t>80.4742mm</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>45.5750mm</t>
+          <t>-17.9250mm</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2167,24 +2167,24 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>180</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>R15</t>
+          <t>R11</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>29.2189mm</t>
+          <t>80.4742mm</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>45.5750mm</t>
+          <t>-21.0467mm</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2194,24 +2194,24 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>180</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>R16</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>31.7189mm</t>
+          <t>89.9764mm</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>45.5650mm</t>
+          <t>36.0857mm</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2221,19 +2221,19 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>R17</t>
+          <t>R13</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>34.2189mm</t>
+          <t>24.2189mm</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2255,17 +2255,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>R18</t>
+          <t>R14</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>20.4231mm</t>
+          <t>26.7189mm</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>-3.3763mm</t>
+          <t>45.5750mm</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2275,24 +2275,24 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>R19</t>
+          <t>R15</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>76.8064mm</t>
+          <t>29.2189mm</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>5.5750mm</t>
+          <t>45.5750mm</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2302,24 +2302,24 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R16</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>18.1501mm</t>
+          <t>31.7189mm</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>44.5248mm</t>
+          <t>45.5650mm</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2329,24 +2329,24 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R17</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>30.1398mm</t>
+          <t>34.2189mm</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>1.9487mm</t>
+          <t>45.5750mm</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2356,24 +2356,24 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>R4</t>
+          <t>R18</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>9.7089mm</t>
+          <t>14.7189mm</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>-16.4250mm</t>
+          <t>4.5850mm</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2383,24 +2383,24 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>R19</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>3.0686mm</t>
+          <t>90.4764mm</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>4.9674mm</t>
+          <t>5.5857mm</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2417,17 +2417,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>R6</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>37.7885mm</t>
+          <t>22.2089mm</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>36.4263mm</t>
+          <t>41.0750mm</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2437,24 +2437,24 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>R7</t>
+          <t>R20</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>37.9994mm</t>
+          <t>83.7089mm</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>32.4249mm</t>
+          <t>33.0750mm</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2464,24 +2464,24 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>R8</t>
+          <t>R21</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>42.2289mm</t>
+          <t>81.8889mm</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>-16.1350mm</t>
+          <t>39.0757mm</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>270</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>R9</t>
+          <t>R22</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>47.0389mm</t>
+          <t>82.3789mm</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>-14.1050mm</t>
+          <t>8.0857mm</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2518,24 +2518,24 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>270</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>SW1</t>
+          <t>R23</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>11.2189mm</t>
+          <t>83.7089mm</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>46.8750mm</t>
+          <t>2.5750mm</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2545,24 +2545,24 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>180</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>SW2</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>15.2189mm</t>
+          <t>24.2089mm</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>46.8750mm</t>
+          <t>-7.9250mm</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -2572,24 +2572,24 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>U1</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>10.4889mm</t>
+          <t>31.2189mm</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>32.5750mm</t>
+          <t>-14.4350mm</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -2606,17 +2606,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>U2</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>32.4689mm</t>
+          <t>0.7189mm</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>-8.6750mm</t>
+          <t>4.5850mm</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -2626,24 +2626,24 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>270</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>U3</t>
+          <t>R6</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>31.7189mm</t>
+          <t>35.3472mm</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>34.5750mm</t>
+          <t>35.5645mm</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2653,24 +2653,24 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>U4</t>
+          <t>R7</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>60.8021mm</t>
+          <t>35.5581mm</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>-15.9759mm</t>
+          <t>31.5631mm</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -2687,17 +2687,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>U5</t>
+          <t>R8</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>61.6789mm</t>
+          <t>50.1690mm</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>27.2050mm</t>
+          <t>-14.3761mm</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2707,24 +2707,24 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>180</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>U6</t>
+          <t>R9</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>61.8264mm</t>
+          <t>57.1690mm</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>-3.7050mm</t>
+          <t>-14.3761mm</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -2734,24 +2734,24 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>U7</t>
+          <t>SW1</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>27.2189mm</t>
+          <t>87.7189mm</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>12.5750mm</t>
+          <t>-21.9250mm</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -2761,24 +2761,24 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>270</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>U8</t>
+          <t>SW2</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>41.7192mm</t>
+          <t>94.2189mm</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>-12.2524mm</t>
+          <t>-21.9250mm</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -2788,24 +2788,24 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>270</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>U1</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>6.7189mm</t>
+          <t>10.4889mm</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>6.5750mm</t>
+          <t>30.8250mm</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -2815,34 +2815,250 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
+          <t>U2</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>30.9689mm</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>-6.6750mm</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>U3</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>29.2776mm</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>33.7132mm</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>U4</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>77.1642mm</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>-19.3750mm</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>U5</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>75.3489mm</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>27.2157mm</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>U6</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>75.4964mm</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>-3.6943mm</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>U7</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>38.0389mm</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>15.0500mm</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>U8</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>53.8165mm</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>-13.9261mm</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>U9</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>5.9789mm</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>10.8250mm</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
           <t>Y1</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>31.9605mm</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>-17.3174mm</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>40.1510mm</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>-5.3000mm</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>90</t>
         </is>
       </c>
     </row>

--- a/hardware/luxdmx_CPL.xlsx
+++ b/hardware/luxdmx_CPL.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E98"/>
+  <dimension ref="A1:E94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,12 +478,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>38.8510mm</t>
+          <t>38.7389mm</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-7.9250mm</t>
+          <t>-9.4250mm</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -532,12 +532,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>40.8710mm</t>
+          <t>41.1989mm</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-7.9250mm</t>
+          <t>-9.4250mm</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -608,17 +608,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C15</t>
+          <t>C16</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>23.2189mm</t>
+          <t>76.9142mm</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>34.0750mm</t>
+          <t>-23.4250mm</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -628,24 +628,24 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>180</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C16</t>
+          <t>C17</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>76.9142mm</t>
+          <t>73.9142mm</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-23.4250mm</t>
+          <t>-15.4250mm</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -655,24 +655,24 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C17</t>
+          <t>C18</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>73.9142mm</t>
+          <t>67.7189mm</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-15.4250mm</t>
+          <t>31.0550mm</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -682,24 +682,24 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>270</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C18</t>
+          <t>C19</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>67.7189mm</t>
+          <t>81.7189mm</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>31.0550mm</t>
+          <t>33.5950mm</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -709,24 +709,24 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>C19</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>81.7189mm</t>
+          <t>7.7689mm</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>33.5950mm</t>
+          <t>16.0750mm</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -736,24 +736,24 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C20</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>7.7689mm</t>
+          <t>84.7695mm</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>16.0750mm</t>
+          <t>36.0413mm</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -770,17 +770,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C20</t>
+          <t>C21</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>84.7695mm</t>
+          <t>65.7439mm</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>36.0413mm</t>
+          <t>34.0750mm</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -790,24 +790,24 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>180</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>C21</t>
+          <t>C22</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>65.7439mm</t>
+          <t>19.7389mm</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>34.0750mm</t>
+          <t>-2.9250mm</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -817,24 +817,24 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C22</t>
+          <t>C23</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>19.7389mm</t>
+          <t>67.7389mm</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-2.9250mm</t>
+          <t>1.0750mm</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -844,24 +844,24 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>180</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C23</t>
+          <t>C24</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>67.7389mm</t>
+          <t>81.7189mm</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.0750mm</t>
+          <t>2.5750mm</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -871,24 +871,24 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C24</t>
+          <t>C25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>81.7189mm</t>
+          <t>85.2089mm</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2.5750mm</t>
+          <t>5.4048mm</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -898,24 +898,24 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C25</t>
+          <t>C26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>85.2089mm</t>
+          <t>66.2439mm</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>5.4048mm</t>
+          <t>4.1000mm</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -925,24 +925,24 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>180</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C26</t>
+          <t>C27</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>66.2439mm</t>
+          <t>21.5189mm</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>4.1000mm</t>
+          <t>13.0500mm</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -959,17 +959,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>C27</t>
+          <t>C28</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>21.5189mm</t>
+          <t>30.7689mm</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>13.0500mm</t>
+          <t>3.5500mm</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -986,17 +986,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>C28</t>
+          <t>C29</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>30.7689mm</t>
+          <t>13.7189mm</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>3.5500mm</t>
+          <t>15.5750mm</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1006,24 +1006,24 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>270</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>C29</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>13.7189mm</t>
+          <t>2.2491mm</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>15.5750mm</t>
+          <t>15.9635mm</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1033,24 +1033,24 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C30</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2.2491mm</t>
+          <t>4.2189mm</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>15.9635mm</t>
+          <t>5.4103mm</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1060,19 +1060,19 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>270</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>C30</t>
+          <t>C31</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>4.2189mm</t>
+          <t>8.2189mm</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1094,17 +1094,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>C31</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>8.2189mm</t>
+          <t>34.1989mm</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>5.4103mm</t>
+          <t>-13.4250mm</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1114,14 +1114,14 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C5</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-13.4250mm</t>
+          <t>-14.4250mm</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1148,17 +1148,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C6</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>34.1989mm</t>
+          <t>32.2189mm</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-14.4250mm</t>
+          <t>-14.4050mm</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1168,24 +1168,24 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>270</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>C6</t>
+          <t>C8</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>32.2189mm</t>
+          <t>24.2389mm</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>-14.4050mm</t>
+          <t>-5.4250mm</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1195,24 +1195,24 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>180</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>C8</t>
+          <t>C9</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>24.2389mm</t>
+          <t>28.7189mm</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>-5.4250mm</t>
+          <t>-14.4050mm</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1222,24 +1222,24 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>270</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>C9</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>28.7189mm</t>
+          <t>88.3264mm</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>-14.4050mm</t>
+          <t>32.0357mm</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1249,24 +1249,24 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>180</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>D10</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>88.3264mm</t>
+          <t>53.2189mm</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>32.0357mm</t>
+          <t>20.0500mm</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1276,24 +1276,24 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>270</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>D10</t>
+          <t>D11</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>53.2189mm</t>
+          <t>65.9642mm</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>20.0500mm</t>
+          <t>-21.4250mm</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1310,17 +1310,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>D11</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>65.9642mm</t>
+          <t>24.1810mm</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>-21.4250mm</t>
+          <t>48.5450mm</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1337,17 +1337,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>D3</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>24.1810mm</t>
+          <t>26.6905mm</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>48.5450mm</t>
+          <t>48.5525mm</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1364,17 +1364,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>D3</t>
+          <t>D4</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>26.6905mm</t>
+          <t>29.2000mm</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>48.5525mm</t>
+          <t>48.5600mm</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1391,17 +1391,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>D4</t>
+          <t>D5</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>29.2000mm</t>
+          <t>31.7094mm</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>48.5600mm</t>
+          <t>48.5675mm</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1418,17 +1418,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>D5</t>
+          <t>D6</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>31.7094mm</t>
+          <t>34.2189mm</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>48.5675mm</t>
+          <t>48.5750mm</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1445,17 +1445,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>D6</t>
+          <t>D7</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>34.2189mm</t>
+          <t>88.9514mm</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>48.5750mm</t>
+          <t>1.0857mm</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1465,24 +1465,24 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>180</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>D7</t>
+          <t>F1</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>88.9514mm</t>
+          <t>54.6189mm</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1.0857mm</t>
+          <t>-20.4250mm</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1499,17 +1499,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>F2</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>54.6189mm</t>
+          <t>95.7189mm</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>-20.4250mm</t>
+          <t>36.1050mm</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1519,14 +1519,14 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>F2</t>
+          <t>F3</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>36.1050mm</t>
+          <t>27.0450mm</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1553,7 +1553,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>F3</t>
+          <t>F4</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>27.0450mm</t>
+          <t>5.0450mm</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1580,7 +1580,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>5.0450mm</t>
+          <t>-4.4550mm</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1607,17 +1607,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>F5</t>
+          <t>FB1</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>95.7189mm</t>
+          <t>66.2189mm</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>-4.4550mm</t>
+          <t>36.5750mm</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1627,24 +1627,24 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>180</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>FB1</t>
+          <t>FB2</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>66.2189mm</t>
+          <t>83.7814mm</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>36.5750mm</t>
+          <t>31.0750mm</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1661,17 +1661,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>FB2</t>
+          <t>FB3</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>83.7814mm</t>
+          <t>84.1564mm</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>31.0750mm</t>
+          <t>0.5750mm</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1688,17 +1688,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>FB3</t>
+          <t>J1</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>84.1564mm</t>
+          <t>108.7189mm</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>0.5750mm</t>
+          <t>29.0750mm</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1708,24 +1708,24 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>270</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>J1</t>
+          <t>J2</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>108.7189mm</t>
+          <t>44.5289mm</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>29.0750mm</t>
+          <t>-22.2186mm</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1735,24 +1735,24 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>J2</t>
+          <t>J3</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>44.5289mm</t>
+          <t>8.9589mm</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>-22.2186mm</t>
+          <t>-6.4250mm</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1769,17 +1769,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>J3</t>
+          <t>J4</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>8.9589mm</t>
+          <t>45.2189mm</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>-6.4250mm</t>
+          <t>33.0750mm</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1789,24 +1789,24 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>J4</t>
+          <t>J5</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>15.4189mm</t>
+          <t>108.8764mm</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>46.7000mm</t>
+          <t>-1.9250mm</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1816,24 +1816,24 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>270</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>J5</t>
+          <t>J6</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>108.8764mm</t>
+          <t>36.2189mm</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>-1.9250mm</t>
+          <t>33.0750mm</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1850,17 +1850,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>J6</t>
+          <t>J7</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>51.9189mm</t>
+          <t>89.7189mm</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>34.2000mm</t>
+          <t>25.0750mm</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1870,24 +1870,24 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>J7</t>
+          <t>J8</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>89.7189mm</t>
+          <t>89.4189mm</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>25.0750mm</t>
+          <t>-6.0393mm</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1904,17 +1904,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>J8</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>89.4189mm</t>
+          <t>72.4642mm</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>-6.0393mm</t>
+          <t>-19.4250mm</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1924,24 +1924,24 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>72.4642mm</t>
+          <t>89.9389mm</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>-19.4250mm</t>
+          <t>39.0750mm</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1951,24 +1951,24 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>89.9389mm</t>
+          <t>90.3889mm</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>39.0750mm</t>
+          <t>8.0857mm</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1985,17 +1985,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>PS1</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>90.3889mm</t>
+          <t>74.5789mm</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>8.0857mm</t>
+          <t>35.5857mm</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2012,17 +2012,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>PS1</t>
+          <t>PS2</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>74.5789mm</t>
+          <t>74.9364mm</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>35.5857mm</t>
+          <t>5.2557mm</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2039,17 +2039,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>PS2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>74.9364mm</t>
+          <t>2.2089mm</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>5.2557mm</t>
+          <t>17.3250mm</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2066,17 +2066,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>R10</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>40.2276mm</t>
+          <t>80.4742mm</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>36.6507mm</t>
+          <t>-17.9250mm</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2086,24 +2086,24 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>180</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>R11</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>40.2276mm</t>
+          <t>80.4742mm</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>31.1507mm</t>
+          <t>-21.0467mm</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2113,24 +2113,24 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>180</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2.2089mm</t>
+          <t>89.9764mm</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>17.3250mm</t>
+          <t>36.0857mm</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2147,17 +2147,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>R10</t>
+          <t>R13</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>80.4742mm</t>
+          <t>24.2189mm</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>-17.9250mm</t>
+          <t>45.5750mm</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2167,24 +2167,24 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>R11</t>
+          <t>R14</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>80.4742mm</t>
+          <t>26.7189mm</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>-21.0467mm</t>
+          <t>45.5750mm</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2194,24 +2194,24 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>R15</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>89.9764mm</t>
+          <t>29.2189mm</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>36.0857mm</t>
+          <t>45.5750mm</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2221,24 +2221,24 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>R13</t>
+          <t>R16</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>24.2189mm</t>
+          <t>31.7189mm</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>45.5750mm</t>
+          <t>45.5650mm</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2255,12 +2255,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>R14</t>
+          <t>R17</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>26.7189mm</t>
+          <t>34.2189mm</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2282,17 +2282,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>R15</t>
+          <t>R18</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>29.2189mm</t>
+          <t>14.7189mm</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>45.5750mm</t>
+          <t>4.5850mm</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2309,17 +2309,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>R16</t>
+          <t>R19</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>31.7189mm</t>
+          <t>90.4764mm</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>45.5650mm</t>
+          <t>5.5857mm</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2329,24 +2329,24 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>R17</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>34.2189mm</t>
+          <t>22.2089mm</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>45.5750mm</t>
+          <t>41.0750mm</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2356,24 +2356,24 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>R18</t>
+          <t>R20</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>14.7189mm</t>
+          <t>83.7089mm</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>4.5850mm</t>
+          <t>33.0750mm</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2383,24 +2383,24 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>R19</t>
+          <t>R21</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>90.4764mm</t>
+          <t>81.8889mm</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>5.5857mm</t>
+          <t>39.0757mm</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2410,24 +2410,24 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>270</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R22</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>22.2089mm</t>
+          <t>82.3789mm</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>41.0750mm</t>
+          <t>8.0857mm</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2437,14 +2437,14 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>270</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>R20</t>
+          <t>R23</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>33.0750mm</t>
+          <t>2.5750mm</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2464,24 +2464,24 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>180</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>R21</t>
+          <t>R24</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>81.8889mm</t>
+          <t>10.7189mm</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>39.0757mm</t>
+          <t>8.5650mm</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2498,17 +2498,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>R22</t>
+          <t>R25</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>82.3789mm</t>
+          <t>13.2189mm</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>8.0857mm</t>
+          <t>8.5650mm</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2518,24 +2518,24 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>R23</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>83.7089mm</t>
+          <t>24.2089mm</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2.5750mm</t>
+          <t>-7.9250mm</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2545,24 +2545,24 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>24.2089mm</t>
+          <t>31.2189mm</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>-7.9250mm</t>
+          <t>-14.4350mm</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -2572,24 +2572,24 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>R4</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>31.2189mm</t>
+          <t>0.7189mm</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>-14.4350mm</t>
+          <t>4.5850mm</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -2599,24 +2599,24 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>270</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>R8</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0.7189mm</t>
+          <t>50.1690mm</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>4.5850mm</t>
+          <t>-14.3761mm</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -2626,24 +2626,24 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>180</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>R6</t>
+          <t>R9</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>35.3472mm</t>
+          <t>57.1690mm</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>35.5645mm</t>
+          <t>-14.3761mm</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2653,24 +2653,24 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>R7</t>
+          <t>SW1</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>35.5581mm</t>
+          <t>84.7189mm</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>31.5631mm</t>
+          <t>-21.9250mm</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -2680,24 +2680,24 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>270</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>R8</t>
+          <t>SW2</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>50.1690mm</t>
+          <t>99.2189mm</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>-14.3761mm</t>
+          <t>-21.9250mm</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2707,24 +2707,24 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>270</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>R9</t>
+          <t>U1</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>57.1690mm</t>
+          <t>10.4889mm</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>-14.3761mm</t>
+          <t>30.8250mm</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -2734,24 +2734,24 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>SW1</t>
+          <t>U2</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>87.7189mm</t>
+          <t>30.9689mm</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>-21.9250mm</t>
+          <t>-6.6750mm</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -2768,17 +2768,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>SW2</t>
+          <t>U4</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>94.2189mm</t>
+          <t>77.1642mm</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>-21.9250mm</t>
+          <t>-19.3750mm</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -2788,24 +2788,24 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>180</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>U1</t>
+          <t>U5</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>10.4889mm</t>
+          <t>75.3489mm</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>30.8250mm</t>
+          <t>27.2157mm</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -2815,24 +2815,24 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>270</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>U2</t>
+          <t>U6</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>30.9689mm</t>
+          <t>75.4964mm</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>-6.6750mm</t>
+          <t>-3.6943mm</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -2849,17 +2849,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>U3</t>
+          <t>U7</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>29.2776mm</t>
+          <t>38.0389mm</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>33.7132mm</t>
+          <t>15.0500mm</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -2869,24 +2869,24 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>U4</t>
+          <t>U8</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>77.1642mm</t>
+          <t>53.8165mm</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>-19.3750mm</t>
+          <t>-13.9261mm</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -2896,24 +2896,24 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>U5</t>
+          <t>U9</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>75.3489mm</t>
+          <t>5.9789mm</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>27.2157mm</t>
+          <t>10.8250mm</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -2923,24 +2923,24 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>U6</t>
+          <t>Y1</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>75.4964mm</t>
+          <t>39.8189mm</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>-3.6943mm</t>
+          <t>-6.2750mm</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -2950,115 +2950,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>270</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>U7</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>38.0389mm</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>15.0500mm</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
           <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>U8</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>53.8165mm</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>-13.9261mm</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>U9</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>5.9789mm</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>10.8250mm</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Y1</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>40.1510mm</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>-5.3000mm</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>90</t>
         </is>
       </c>
     </row>
